--- a/samples/clover/design-data/xlsx/Const.xlsx
+++ b/samples/clover/design-data/xlsx/Const.xlsx
@@ -14,14 +14,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Run!$B$2:$E$12]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Const_Score!$B$2:$E$6]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Const_Economy!$B$2:$E$16]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Const_Economy!$B$2:$E$19]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[RngStream!$B$2:$C$14]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="106">
   <si>
     <t xml:space="preserve">:const RunConst</t>
   </si>
@@ -219,6 +219,24 @@
   </si>
   <si>
     <t xml:space="preserve">상점의 팩 칸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PackEnhanceChanceBp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">표준 팩의 카드 한 장이 강화를 달고 나올 확률 (만분율)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PackSealChanceBp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">표준 팩의 카드 한 장이 인장을 달고 나올 확률 (만분율)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PackEditionChanceBp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">표준 팩의 카드 한 장이 에디션을 달고 나올 확률 (만분율)</t>
   </si>
   <si>
     <t xml:space="preserve">SoulChanceNum</t>
@@ -808,14 +826,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.609375" customWidth="1"/>
-    <col min="2" max="2" width="22.265625" customWidth="1"/>
+    <col min="1" max="2" width="24.609375" customWidth="1"/>
     <col min="3" max="3" width="7.03125" customWidth="1"/>
     <col min="4" max="4" width="8.203125" customWidth="1"/>
-    <col min="5" max="5" width="36.328125" customWidth="1"/>
+    <col min="5" max="5" width="41.015625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1022,7 +1039,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="5">
-        <v>3</v>
+        <v>2000</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>67</v>
@@ -1042,8 +1059,50 @@
         <v>69</v>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="5">
+        <v>800</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="6">
+        <v>3</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:E16"/>
+  <autoFilter ref="B2:E19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1060,10 +1119,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C1" s="2"/>
     </row>
@@ -1072,112 +1131,112 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Const.xlsx
+++ b/samples/clover/design-data/xlsx/Const.xlsx
@@ -176,31 +176,31 @@
     <t xml:space="preserve">LegendaryBaseCost</t>
   </si>
   <si>
-    <t xml:space="preserve">전설 조커는 값이 없으므로 판매가의 기준이 이것입니다</t>
+    <t xml:space="preserve">전설 조커는 가격이 없으므로 판매가의 기준이 이것입니다</t>
   </si>
   <si>
     <t xml:space="preserve">TarotCost</t>
   </si>
   <si>
-    <t xml:space="preserve">상점의 타로 값</t>
+    <t xml:space="preserve">상점의 타로 가격</t>
   </si>
   <si>
     <t xml:space="preserve">PlanetCost</t>
   </si>
   <si>
-    <t xml:space="preserve">상점의 행성 값</t>
+    <t xml:space="preserve">상점의 행성 가격</t>
   </si>
   <si>
     <t xml:space="preserve">SpectralCost</t>
   </si>
   <si>
-    <t xml:space="preserve">상점의 유령 값</t>
+    <t xml:space="preserve">상점의 유령 가격</t>
   </si>
   <si>
     <t xml:space="preserve">PlayingCardCost</t>
   </si>
   <si>
-    <t xml:space="preserve">상점의 플레잉 카드 값</t>
+    <t xml:space="preserve">상점의 플레잉 카드 가격</t>
   </si>
   <si>
     <t xml:space="preserve">VoucherCost</t>

--- a/samples/clover/design-data/xlsx/Const.xlsx
+++ b/samples/clover/design-data/xlsx/Const.xlsx
@@ -14,14 +14,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Run!$B$2:$E$12]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Const_Score!$B$2:$E$6]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Const_Economy!$B$2:$E$19]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Const_Economy!$B$2:$E$21]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[RngStream!$B$2:$C$14]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
   <si>
     <t xml:space="preserve">:const RunConst</t>
   </si>
@@ -249,6 +249,18 @@
   </si>
   <si>
     <t xml:space="preserve">`The Soul` 이 나올 확률의 분모</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoneyPerHandLeft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드 종료 시 남은 핸드 하나마다 받는 금액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoneyPerDiscardLeft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라운드 종료 시 남은 버리기 하나마다 받는 금액</t>
   </si>
   <si>
     <t xml:space="preserve">:table RngStream(key=stream)</t>
@@ -826,7 +838,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="24.609375" customWidth="1"/>
@@ -1101,8 +1113,36 @@
         <v>75</v>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:E19"/>
+  <autoFilter ref="B2:E21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1119,10 +1159,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C1" s="2"/>
     </row>
@@ -1131,112 +1171,112 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Const.xlsx
+++ b/samples/clover/design-data/xlsx/Const.xlsx
@@ -15,13 +15,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Run!$B$2:$E$12]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Const_Score!$B$2:$E$6]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Const_Economy!$B$2:$E$21]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[RngStream!$B$2:$C$14]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[RngStream!$B$2:$C$15]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
   <si>
     <t xml:space="preserve">:const RunConst</t>
   </si>
@@ -351,6 +351,12 @@
   </si>
   <si>
     <t xml:space="preserve">`smudge` 의 난수 배수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sticker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스테이크가 붙이는 스티커</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.15625" customWidth="1"/>
@@ -1279,8 +1285,16 @@
         <v>109</v>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:C14"/>
+  <autoFilter ref="B2:C15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/samples/clover/design-data/xlsx/Const.xlsx
+++ b/samples/clover/design-data/xlsx/Const.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">:const ScoreConst</t>
   </si>
   <si>
-    <t xml:space="preserve">득점의 단위와 규격입니다. **두 구현이 같아야 하는 값들입니다.**</t>
+    <t xml:space="preserve">득점의 단위와 규격입니다. **코드가 아니라 여기 있어야 하는 값들입니다.**</t>
   </si>
   <si>
     <t xml:space="preserve">MultScale</t>
@@ -746,7 +746,7 @@
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.265625" customWidth="1"/>
-    <col min="2" max="2" width="46.875" customWidth="1"/>
+    <col min="2" max="2" width="52.734375" customWidth="1"/>
     <col min="3" max="3" width="7.03125" customWidth="1"/>
     <col min="4" max="4" width="8.203125" customWidth="1"/>
     <col min="5" max="5" width="37.5" customWidth="1"/>
